--- a/TestData/TMTI0027313_VerifyCFIndustryGroupUpdatedToTECHonOpportunities.xlsx
+++ b/TestData/TMTI0027313_VerifyCFIndustryGroupUpdatedToTECHonOpportunities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7129DAD9-C841-40CA-95D8-877A6D7B2A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84812094-CA56-4F49-B73D-60FAF49EA158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>General Financial Advisory</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -288,6 +285,9 @@
   </si>
   <si>
     <t>QuickLink</t>
+  </si>
+  <si>
+    <t>CSDN-0000001546</t>
   </si>
 </sst>
 </file>
@@ -1029,13 +1029,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1059,17 +1059,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -1084,65 +1084,65 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1156,22 +1156,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA6523B-6FB8-485B-A032-B6DB9A33E644}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1185,105 +1185,105 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790F47CA-119E-4C77-A2BA-C6AC561DC45F}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1294,85 +1294,85 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
       </c>
       <c r="N2" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" t="s">
         <v>28</v>
       </c>
-      <c r="S2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="V2" t="s">
+        <v>29</v>
+      </c>
+      <c r="W2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="U2" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AB2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC2" t="s">
         <v>34</v>
       </c>
-      <c r="AA2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>35</v>
-      </c>
       <c r="AD2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1383,44 +1383,44 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB0541C-F2E2-46E6-A5D0-1C56A6B4FD74}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>72</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>73</v>
       </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1431,19 +1431,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2312EA66-75D5-4B8A-A0C1-B1C83049089C}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1455,33 +1455,33 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8C51AF-DEAB-411D-999C-276DD13EBE95}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>80</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>81</v>
-      </c>
-      <c r="C2" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1492,19 +1492,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF2DDDA-B9CA-4C91-BCF4-5D41594CC8DD}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
